--- a/artfynd/A 26423-2026 artfynd.xlsx
+++ b/artfynd/A 26423-2026 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>91697700</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479148.9778899814</v>
+        <v>479149</v>
       </c>
       <c r="R2" t="n">
-        <v>6297787.333016623</v>
+        <v>6297787</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>

--- a/artfynd/A 26423-2026 artfynd.xlsx
+++ b/artfynd/A 26423-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,8 +792,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91697700</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26423-2026 artfynd.xlsx
+++ b/artfynd/A 26423-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91697700</v>
+        <v>135941365</v>
       </c>
       <c r="B2" t="n">
-        <v>57950</v>
+        <v>96466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +691,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>530</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dichelyma capillaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L. ex Dicks.) Myrin</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Madsjö v., Sm</t>
+          <t>Mad sjö, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479149</v>
+        <v>479243</v>
       </c>
       <c r="R2" t="n">
-        <v>6297787</v>
+        <v>6297704</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,22 +757,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-03-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-03-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,22 +771,153 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>strand</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>ved</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caroline Mortlock</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Caroline Mortlock</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135941365</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>91697700</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Madsjö v., Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>479149</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6297787</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-03-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-03-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/91697700</t>
         </is>
@@ -801,6 +926,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26423-2026 artfynd.xlsx
+++ b/artfynd/A 26423-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135941365</v>
       </c>
       <c r="B2" t="n">
-        <v>96466</v>
+        <v>96483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26423-2026 artfynd.xlsx
+++ b/artfynd/A 26423-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135941365</v>
       </c>
       <c r="B2" t="n">
-        <v>96483</v>
+        <v>96484</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26423-2026 artfynd.xlsx
+++ b/artfynd/A 26423-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135941365</v>
       </c>
       <c r="B2" t="n">
-        <v>96484</v>
+        <v>96485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26423-2026 artfynd.xlsx
+++ b/artfynd/A 26423-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135941365</v>
       </c>
       <c r="B2" t="n">
-        <v>96485</v>
+        <v>96486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26423-2026 artfynd.xlsx
+++ b/artfynd/A 26423-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135941365</v>
       </c>
       <c r="B2" t="n">
-        <v>96486</v>
+        <v>96492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26423-2026 artfynd.xlsx
+++ b/artfynd/A 26423-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135941365</v>
       </c>
       <c r="B2" t="n">
-        <v>96492</v>
+        <v>96493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26423-2026 artfynd.xlsx
+++ b/artfynd/A 26423-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135941365</v>
       </c>
       <c r="B2" t="n">
-        <v>96493</v>
+        <v>96504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26423-2026 artfynd.xlsx
+++ b/artfynd/A 26423-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135941365</v>
       </c>
       <c r="B2" t="n">
-        <v>96504</v>
+        <v>96517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26423-2026 artfynd.xlsx
+++ b/artfynd/A 26423-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135941365</v>
       </c>
       <c r="B2" t="n">
-        <v>96517</v>
+        <v>96518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26423-2026 artfynd.xlsx
+++ b/artfynd/A 26423-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135941365</v>
       </c>
       <c r="B2" t="n">
-        <v>96518</v>
+        <v>96531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26423-2026 artfynd.xlsx
+++ b/artfynd/A 26423-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135941365</v>
       </c>
       <c r="B2" t="n">
-        <v>96531</v>
+        <v>96532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
